--- a/astro-site/public/dl/kit-tareas-heladeria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -136,47 +138,47 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -536,15 +538,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -552,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -580,9 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -611,8 +613,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -621,17 +640,17 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="16"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,6 +667,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -968,6 +988,7 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="11" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
@@ -982,10 +1003,19 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-heladeria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/BONUS-02-calendario-anual-tareas.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -615,9 +615,38 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Fechas del calendario:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Las fechas nacionales están puestas para España: Día del Padre (19 de marzo), comuniones (abril-junio), Día de la Madre (primer domingo de mayo), San Juan, 15 de agosto, 1 de noviembre y el puente del 6-8 de diciembre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Cambia las que no apliquen en tu comunidad y añade las fiestas patronales de tu ciudad: son las que mueven una heladería de barrio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -756,7 +785,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Semana Santa: sabores temáticos (torrija, mona). Preparar temporada alta: stock, equipo.</t>
+          <t>Semana Santa: sabores temáticos (torrija, mona). 19 de marzo, Día del Padre: tartas heladas por encargo. Preparar temporada alta: stock, equipo.</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -780,7 +809,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Inicio primavera: ampliar carta con frutales. Reforzar equipo, formación.</t>
+          <t>Inicio primavera: ampliar carta con frutales. Arranca la campaña de COMUNIONES (abril-junio): tartas heladas y catering, con señal y encargos cerrados 2 semanas antes. Reforzar equipo, formación.</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -804,7 +833,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Inicio temporada alta. Carta completa 18-24 sabores. Abrir terraza.</t>
+          <t>Inicio temporada alta. Carta completa 18-24 sabores. Abrir terraza. Día de la Madre (primer domingo de mayo) y comuniones: tartas heladas por encargo.</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -828,7 +857,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Inicio verano: máxima producción. Día de la Madre: tartas heladas. Campaña RRSS.</t>
+          <t>Inicio verano: máxima producción. Fin de curso y San Juan (23-24): pedidos de grupo y noche larga de terraza. Campaña RRSS.</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -876,7 +905,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Pico de temporada. Stock +50%. Catering eventos de verano.</t>
+          <t>Pico de temporada. Stock +50%. 15 de agosto (Asunción), festivo nacional y día grande de muchas fiestas patronales. Catering eventos de verano.</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -948,7 +977,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Temporada baja. Productos complementarios: chocolate caliente, gofres. Mantenimiento.</t>
+          <t>Temporada baja. 1 de noviembre (Todos los Santos), festivo: con buen tiempo sigue siendo día de terraza. Productos complementarios: chocolate caliente, gofres. Mantenimiento.</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -972,7 +1001,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Navidad: turrón, polvorón, edición limitada. Catering empresas fin de año. Tartas heladas.</t>
+          <t>Puente del 6-8 de diciembre: primer pico de la campaña. Navidad: turrón, polvorón, edición limitada. Catering empresas fin de año. Tartas heladas.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1003,8 +1032,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
